--- a/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/year-volumes/1882.xlsx
+++ b/rtss-pre1917/src/main/resources/csk-dvizhenie-evropriskoi-chasti-rossii/year-volumes/1882.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\github\RTSS\rtss-pre1917\src\main\resources\csk-dvizhenie-evropriskoi-chasti-rossii\year-volumes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B6C7E28-A984-476B-A04C-3AD917810812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF59C988-17A0-4F05-9323-6ADD1FBD076F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -237,7 +237,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -246,6 +246,11 @@
       <b/>
       <sz val="11"/>
       <name val="Carlito"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -287,22 +292,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -310,6 +306,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -532,43 +537,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L1" s="10" t="s">
+      <c r="L1" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="M1" s="10" t="s">
+      <c r="M1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="7" t="s">
         <v>63</v>
       </c>
     </row>
@@ -576,28 +581,28 @@
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="5">
+      <c r="B2" s="4">
         <v>6484</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="4">
         <v>6128</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2" s="4">
         <v>12612</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="4">
         <v>4379</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="4">
         <v>4159</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="4">
         <v>8538</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="5">
         <v>105.8</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="5">
         <v>147.69999999999999</v>
       </c>
       <c r="K2" s="1">
@@ -621,28 +626,28 @@
       <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5">
+      <c r="B3" s="4">
         <v>13724</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="4">
         <v>13067</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3" s="4">
         <v>26791</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="4">
         <v>9322</v>
       </c>
-      <c r="F3" s="5">
+      <c r="F3" s="4">
         <v>8591</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="4">
         <v>17913</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="5">
         <v>105</v>
       </c>
-      <c r="I3" s="6">
+      <c r="I3" s="5">
         <v>149.6</v>
       </c>
       <c r="K3" s="1">
@@ -666,28 +671,28 @@
       <c r="A4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="5">
+      <c r="B4" s="4">
         <v>35534</v>
       </c>
-      <c r="C4" s="5">
+      <c r="C4" s="4">
         <v>32923</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>68457</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>24143</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>22050</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>46193</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="5">
         <v>107.9</v>
       </c>
-      <c r="I4" s="6">
+      <c r="I4" s="5">
         <v>148.19999999999999</v>
       </c>
       <c r="K4" s="1">
@@ -711,28 +716,28 @@
       <c r="A5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="4">
         <v>25440</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>23828</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>49268</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>18208</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>16743</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>34951</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="5">
         <v>106.8</v>
       </c>
-      <c r="I5" s="6">
+      <c r="I5" s="5">
         <v>141</v>
       </c>
       <c r="K5" s="1">
@@ -756,28 +761,28 @@
       <c r="A6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="4">
         <v>25620</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="4">
         <v>23693</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>49313</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="4">
         <v>18201</v>
       </c>
-      <c r="F6" s="5">
+      <c r="F6" s="4">
         <v>16665</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="4">
         <v>34866</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <v>108.1</v>
       </c>
-      <c r="I6" s="6">
+      <c r="I6" s="5">
         <v>141.4</v>
       </c>
       <c r="K6" s="1">
@@ -801,28 +806,28 @@
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="4">
         <v>36697</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="4">
         <v>34763</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>71460</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="4">
         <v>33212</v>
       </c>
-      <c r="F7" s="5">
+      <c r="F7" s="4">
         <v>31841</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="4">
         <v>65053</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="5">
         <v>105.6</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="5">
         <v>109.8</v>
       </c>
       <c r="K7" s="1">
@@ -846,28 +851,28 @@
       <c r="A8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="4">
         <v>28489</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="4">
         <v>27415</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>55904</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="4">
         <v>19522</v>
       </c>
-      <c r="F8" s="5">
+      <c r="F8" s="4">
         <v>18651</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="4">
         <v>38173</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="5">
         <v>103.9</v>
       </c>
-      <c r="I8" s="6">
+      <c r="I8" s="5">
         <v>146.4</v>
       </c>
       <c r="K8" s="1">
@@ -891,28 +896,28 @@
       <c r="A9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="5">
+      <c r="B9" s="4">
         <v>55339</v>
       </c>
-      <c r="C9" s="5">
+      <c r="C9" s="4">
         <v>51354</v>
       </c>
-      <c r="D9" s="5">
+      <c r="D9" s="4">
         <v>106693</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="4">
         <v>40944</v>
       </c>
-      <c r="F9" s="5">
+      <c r="F9" s="4">
         <v>38508</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="4">
         <v>79452</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="5">
         <v>107.8</v>
       </c>
-      <c r="I9" s="6">
+      <c r="I9" s="5">
         <v>134.30000000000001</v>
       </c>
       <c r="K9" s="1">
@@ -936,28 +941,28 @@
       <c r="A10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="5">
+      <c r="B10" s="4">
         <v>64615</v>
       </c>
-      <c r="C10" s="5">
+      <c r="C10" s="4">
         <v>62544</v>
       </c>
-      <c r="D10" s="5">
+      <c r="D10" s="4">
         <v>127159</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="4">
         <v>61086</v>
       </c>
-      <c r="F10" s="5">
+      <c r="F10" s="4">
         <v>58961</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>120047</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="5">
         <v>103.3</v>
       </c>
-      <c r="I10" s="6">
+      <c r="I10" s="5">
         <v>105.9</v>
       </c>
       <c r="K10" s="1">
@@ -981,28 +986,28 @@
       <c r="A11" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="4">
         <v>80579</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="4">
         <v>77210</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>157789</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="4">
         <v>58738</v>
       </c>
-      <c r="F11" s="5">
+      <c r="F11" s="4">
         <v>55539</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>114277</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="5">
         <v>104.4</v>
       </c>
-      <c r="I11" s="6">
+      <c r="I11" s="5">
         <v>138.1</v>
       </c>
       <c r="K11" s="1">
@@ -1026,28 +1031,28 @@
       <c r="A12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="4">
         <v>28693</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="4">
         <v>25914</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>54607</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E12" s="4">
         <v>23147</v>
       </c>
-      <c r="F12" s="5">
+      <c r="F12" s="4">
         <v>22165</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>45312</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <v>110.7</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I12" s="5">
         <v>120.5</v>
       </c>
       <c r="K12" s="1">
@@ -1071,28 +1076,28 @@
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="5">
+      <c r="B13" s="4">
         <v>43609</v>
       </c>
-      <c r="C13" s="5">
+      <c r="C13" s="4">
         <v>41550</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>85159</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>28941</v>
       </c>
-      <c r="F13" s="5">
+      <c r="F13" s="4">
         <v>27014</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>55955</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <v>105</v>
       </c>
-      <c r="I13" s="6">
+      <c r="I13" s="5">
         <v>152.19999999999999</v>
       </c>
       <c r="K13" s="1">
@@ -1116,28 +1121,28 @@
       <c r="A14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B14" s="4">
         <v>47614</v>
       </c>
-      <c r="C14" s="5">
+      <c r="C14" s="4">
         <v>45102</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>92716</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="4">
         <v>33897</v>
       </c>
-      <c r="F14" s="5">
+      <c r="F14" s="4">
         <v>30753</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>64650</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <v>105.6</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I14" s="5">
         <v>130.69999999999999</v>
       </c>
       <c r="K14" s="1">
@@ -1161,28 +1166,28 @@
       <c r="A15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B15" s="5">
+      <c r="B15" s="4">
         <v>49430</v>
       </c>
-      <c r="C15" s="5">
+      <c r="C15" s="4">
         <v>47369</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>96799</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="4">
         <v>38395</v>
       </c>
-      <c r="F15" s="5">
+      <c r="F15" s="4">
         <v>36502</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>74897</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <v>104.3</v>
       </c>
-      <c r="I15" s="6">
+      <c r="I15" s="5">
         <v>129.19999999999999</v>
       </c>
       <c r="K15" s="1">
@@ -1206,28 +1211,28 @@
       <c r="A16" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="5">
+      <c r="B16" s="4">
         <v>27451</v>
       </c>
-      <c r="C16" s="5">
+      <c r="C16" s="4">
         <v>26028</v>
       </c>
-      <c r="D16" s="5">
+      <c r="D16" s="4">
         <v>53479</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="4">
         <v>23289</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>21919</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>45208</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <v>105.5</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="5">
         <v>118.3</v>
       </c>
       <c r="K16" s="1">
@@ -1251,28 +1256,28 @@
       <c r="A17" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="5">
+      <c r="B17" s="4">
         <v>77974</v>
       </c>
-      <c r="C17" s="5">
+      <c r="C17" s="4">
         <v>73412</v>
       </c>
-      <c r="D17" s="5">
+      <c r="D17" s="4">
         <v>151386</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="4">
         <v>57773</v>
       </c>
-      <c r="F17" s="5">
+      <c r="F17" s="4">
         <v>53256</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>111029</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <v>106.2</v>
       </c>
-      <c r="I17" s="6">
+      <c r="I17" s="5">
         <v>136.30000000000001</v>
       </c>
       <c r="K17" s="1">
@@ -1296,28 +1301,28 @@
       <c r="A18" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="5">
+      <c r="B18" s="4">
         <v>25399</v>
       </c>
-      <c r="C18" s="5">
+      <c r="C18" s="4">
         <v>23606</v>
       </c>
-      <c r="D18" s="5">
+      <c r="D18" s="4">
         <v>49005</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>20622</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>19675</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>40297</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <v>107.6</v>
       </c>
-      <c r="I18" s="6">
+      <c r="I18" s="5">
         <v>121.6</v>
       </c>
       <c r="K18" s="1">
@@ -1341,28 +1346,28 @@
       <c r="A19" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="5">
+      <c r="B19" s="4">
         <v>30847</v>
       </c>
-      <c r="C19" s="5">
+      <c r="C19" s="4">
         <v>29635</v>
       </c>
-      <c r="D19" s="5">
+      <c r="D19" s="4">
         <v>60482</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="4">
         <v>24195</v>
       </c>
-      <c r="F19" s="5">
+      <c r="F19" s="4">
         <v>23556</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>47751</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <v>104.1</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="5">
         <v>126.7</v>
       </c>
       <c r="K19" s="1">
@@ -1386,28 +1391,28 @@
       <c r="A20" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B20" s="5">
+      <c r="B20" s="4">
         <v>9752</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C20" s="4">
         <v>8901</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D20" s="4">
         <v>18653</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="4">
         <v>7057</v>
       </c>
-      <c r="F20" s="5">
+      <c r="F20" s="4">
         <v>6427</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>13484</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <v>109.6</v>
       </c>
-      <c r="I20" s="6">
+      <c r="I20" s="5">
         <v>138.30000000000001</v>
       </c>
       <c r="K20" s="1">
@@ -1431,28 +1436,28 @@
       <c r="A21" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="4">
         <v>60697</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="4">
         <v>56910</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>117607</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="4">
         <v>57930</v>
       </c>
-      <c r="F21" s="5">
+      <c r="F21" s="4">
         <v>54255</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>112185</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <v>106.7</v>
       </c>
-      <c r="I21" s="6">
+      <c r="I21" s="5">
         <v>104.8</v>
       </c>
       <c r="K21" s="1">
@@ -1476,28 +1481,28 @@
       <c r="A22" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="4">
         <v>19615</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>18308</v>
       </c>
-      <c r="D22" s="5">
+      <c r="D22" s="4">
         <v>37923</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="4">
         <v>14044</v>
       </c>
-      <c r="F22" s="5">
+      <c r="F22" s="4">
         <v>13421</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="4">
         <v>27465</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <v>107.1</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="5">
         <v>138.1</v>
       </c>
       <c r="K22" s="1">
@@ -1521,28 +1526,28 @@
       <c r="A23" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="4">
         <v>37959</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="4">
         <v>34692</v>
       </c>
-      <c r="D23" s="5">
+      <c r="D23" s="4">
         <v>72651</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="4">
         <v>24385</v>
       </c>
-      <c r="F23" s="5">
+      <c r="F23" s="4">
         <v>22443</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="4">
         <v>46828</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <v>109.4</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I23" s="5">
         <v>155.1</v>
       </c>
       <c r="K23" s="1">
@@ -1566,28 +1571,28 @@
       <c r="A24" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="4">
         <v>30870</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>28976</v>
       </c>
-      <c r="D24" s="5">
+      <c r="D24" s="4">
         <v>59846</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="4">
         <v>17698</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="4">
         <v>16541</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="4">
         <v>34239</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <v>106.5</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="5">
         <v>174.8</v>
       </c>
       <c r="K24" s="1">
@@ -1611,28 +1616,28 @@
       <c r="A25" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B25" s="5">
+      <c r="B25" s="4">
         <v>48733</v>
       </c>
-      <c r="C25" s="5">
+      <c r="C25" s="4">
         <v>46185</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>94918</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="4">
         <v>52187</v>
       </c>
-      <c r="F25" s="5">
+      <c r="F25" s="4">
         <v>46936</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="4">
         <v>99123</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <v>105.5</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="5">
         <v>95.8</v>
       </c>
       <c r="K25" s="1">
@@ -1656,28 +1661,28 @@
       <c r="A26" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B26" s="5">
+      <c r="B26" s="4">
         <v>42104</v>
       </c>
-      <c r="C26" s="5">
+      <c r="C26" s="4">
         <v>39992</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>82096</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="4">
         <v>33597</v>
       </c>
-      <c r="F26" s="5">
+      <c r="F26" s="4">
         <v>32579</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="4">
         <v>66176</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="5">
         <v>105.3</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="5">
         <v>124.1</v>
       </c>
       <c r="K26" s="1">
@@ -1701,28 +1706,28 @@
       <c r="A27" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="5">
+      <c r="B27" s="4">
         <v>24498</v>
       </c>
-      <c r="C27" s="5">
+      <c r="C27" s="4">
         <v>23525</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>48023</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="4">
         <v>20521</v>
       </c>
-      <c r="F27" s="5">
+      <c r="F27" s="4">
         <v>19217</v>
       </c>
-      <c r="G27" s="5">
+      <c r="G27" s="4">
         <v>39738</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="5">
         <v>104.1</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="5">
         <v>120.9</v>
       </c>
       <c r="K27" s="1">
@@ -1746,28 +1751,28 @@
       <c r="A28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="5">
+      <c r="B28" s="4">
         <v>7988</v>
       </c>
-      <c r="C28" s="5">
+      <c r="C28" s="4">
         <v>7637</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>15625</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="4">
         <v>6548</v>
       </c>
-      <c r="F28" s="5">
+      <c r="F28" s="4">
         <v>5986</v>
       </c>
-      <c r="G28" s="5">
+      <c r="G28" s="4">
         <v>12534</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="5">
         <v>104.6</v>
       </c>
-      <c r="I28" s="6">
+      <c r="I28" s="5">
         <v>124.6</v>
       </c>
       <c r="K28" s="1">
@@ -1791,28 +1796,28 @@
       <c r="A29" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B29" s="5">
+      <c r="B29" s="4">
         <v>39477</v>
       </c>
-      <c r="C29" s="5">
+      <c r="C29" s="4">
         <v>37368</v>
       </c>
-      <c r="D29" s="5">
+      <c r="D29" s="4">
         <v>76845</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="4">
         <v>30603</v>
       </c>
-      <c r="F29" s="5">
+      <c r="F29" s="4">
         <v>28632</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="4">
         <v>59235</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="5">
         <v>105.6</v>
       </c>
-      <c r="I29" s="6">
+      <c r="I29" s="5">
         <v>129.69999999999999</v>
       </c>
       <c r="K29" s="1">
@@ -1836,28 +1841,28 @@
       <c r="A30" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B30" s="5">
+      <c r="B30" s="4">
         <v>51484</v>
       </c>
-      <c r="C30" s="5">
+      <c r="C30" s="4">
         <v>49509</v>
       </c>
-      <c r="D30" s="5">
+      <c r="D30" s="4">
         <v>100993</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="4">
         <v>45307</v>
       </c>
-      <c r="F30" s="5">
+      <c r="F30" s="4">
         <v>42773</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>88080</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="5">
         <v>103.8</v>
       </c>
-      <c r="I30" s="6">
+      <c r="I30" s="5">
         <v>114.7</v>
       </c>
       <c r="K30" s="1">
@@ -1881,28 +1886,28 @@
       <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B31" s="5">
+      <c r="B31" s="4">
         <v>40665</v>
       </c>
-      <c r="C31" s="5">
+      <c r="C31" s="4">
         <v>38799</v>
       </c>
-      <c r="D31" s="5">
+      <c r="D31" s="4">
         <v>79464</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="4">
         <v>33121</v>
       </c>
-      <c r="F31" s="5">
+      <c r="F31" s="4">
         <v>31382</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="4">
         <v>64503</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="5">
         <v>104.8</v>
       </c>
-      <c r="I31" s="6">
+      <c r="I31" s="5">
         <v>123.2</v>
       </c>
       <c r="K31" s="1">
@@ -1926,28 +1931,28 @@
       <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="5">
+      <c r="B32" s="4">
         <v>76016</v>
       </c>
-      <c r="C32" s="5">
+      <c r="C32" s="4">
         <v>72517</v>
       </c>
-      <c r="D32" s="5">
+      <c r="D32" s="4">
         <v>148533</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="4">
         <v>58427</v>
       </c>
-      <c r="F32" s="5">
+      <c r="F32" s="4">
         <v>54650</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="4">
         <v>113077</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="5">
         <v>104.8</v>
       </c>
-      <c r="I32" s="6">
+      <c r="I32" s="5">
         <v>131.4</v>
       </c>
       <c r="K32" s="1">
@@ -1971,28 +1976,28 @@
       <c r="A33" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B33" s="5">
+      <c r="B33" s="4">
         <v>60336</v>
       </c>
-      <c r="C33" s="5">
+      <c r="C33" s="4">
         <v>56516</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="4">
         <v>116852</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="4">
         <v>43424</v>
       </c>
-      <c r="F33" s="5">
+      <c r="F33" s="4">
         <v>40351</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="4">
         <v>83775</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="5">
         <v>106.8</v>
       </c>
-      <c r="I33" s="6">
+      <c r="I33" s="5">
         <v>139.5</v>
       </c>
       <c r="K33" s="1">
@@ -2016,28 +2021,28 @@
       <c r="A34" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B34" s="5">
+      <c r="B34" s="4">
         <v>64075</v>
       </c>
-      <c r="C34" s="5">
+      <c r="C34" s="4">
         <v>62252</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="4">
         <v>126327</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="4">
         <v>45705</v>
       </c>
-      <c r="F34" s="5">
+      <c r="F34" s="4">
         <v>43252</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <v>88957</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="5">
         <v>102.9</v>
       </c>
-      <c r="I34" s="6">
+      <c r="I34" s="5">
         <v>142</v>
       </c>
       <c r="K34" s="1">
@@ -2061,28 +2066,28 @@
       <c r="A35" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B35" s="5">
+      <c r="B35" s="4">
         <v>22124</v>
       </c>
-      <c r="C35" s="5">
+      <c r="C35" s="4">
         <v>21305</v>
       </c>
-      <c r="D35" s="5">
+      <c r="D35" s="4">
         <v>43429</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="4">
         <v>17703</v>
       </c>
-      <c r="F35" s="5">
+      <c r="F35" s="4">
         <v>16919</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="4">
         <v>34622</v>
       </c>
-      <c r="H35" s="6">
+      <c r="H35" s="5">
         <v>103.8</v>
       </c>
-      <c r="I35" s="6">
+      <c r="I35" s="5">
         <v>125.4</v>
       </c>
       <c r="K35" s="1">
@@ -2106,28 +2111,28 @@
       <c r="A36" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B36" s="5">
+      <c r="B36" s="4">
         <v>45130</v>
       </c>
-      <c r="C36" s="5">
+      <c r="C36" s="4">
         <v>43124</v>
       </c>
-      <c r="D36" s="5">
+      <c r="D36" s="4">
         <v>88254</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="4">
         <v>34799</v>
       </c>
-      <c r="F36" s="5">
+      <c r="F36" s="4">
         <v>32570</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <v>67369</v>
       </c>
-      <c r="H36" s="6">
+      <c r="H36" s="5">
         <v>104.7</v>
       </c>
-      <c r="I36" s="6">
+      <c r="I36" s="5">
         <v>131</v>
       </c>
       <c r="K36" s="1">
@@ -2151,28 +2156,28 @@
       <c r="A37" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B37" s="5">
+      <c r="B37" s="4">
         <v>71419</v>
       </c>
-      <c r="C37" s="5">
+      <c r="C37" s="4">
         <v>67974</v>
       </c>
-      <c r="D37" s="5">
+      <c r="D37" s="4">
         <v>139393</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="4">
         <v>53663</v>
       </c>
-      <c r="F37" s="5">
+      <c r="F37" s="4">
         <v>49515</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="4">
         <v>103178</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37" s="5">
         <v>105.1</v>
       </c>
-      <c r="I37" s="6">
+      <c r="I37" s="5">
         <v>135.1</v>
       </c>
       <c r="K37" s="1">
@@ -2196,28 +2201,28 @@
       <c r="A38" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B38" s="5">
+      <c r="B38" s="4">
         <v>29678</v>
       </c>
-      <c r="C38" s="5">
+      <c r="C38" s="4">
         <v>28038</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="4">
         <v>57716</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="4">
         <v>35768</v>
       </c>
-      <c r="F38" s="5">
+      <c r="F38" s="4">
         <v>28973</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="4">
         <v>64741</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="5">
         <v>105.8</v>
       </c>
-      <c r="I38" s="6">
+      <c r="I38" s="5">
         <v>89.1</v>
       </c>
       <c r="K38" s="1">
@@ -2241,28 +2246,28 @@
       <c r="A39" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B39" s="5">
+      <c r="B39" s="4">
         <v>57268</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="4">
         <v>54032</v>
       </c>
-      <c r="D39" s="5">
+      <c r="D39" s="4">
         <v>111300</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="4">
         <v>46762</v>
       </c>
-      <c r="F39" s="5">
+      <c r="F39" s="4">
         <v>43795</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="4">
         <v>90557</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="5">
         <v>106</v>
       </c>
-      <c r="I39" s="6">
+      <c r="I39" s="5">
         <v>122.9</v>
       </c>
       <c r="K39" s="1">
@@ -2286,28 +2291,28 @@
       <c r="A40" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B40" s="5">
+      <c r="B40" s="4">
         <v>36851</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C40" s="4">
         <v>35662</v>
       </c>
-      <c r="D40" s="5">
+      <c r="D40" s="4">
         <v>72513</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="4">
         <v>31390</v>
       </c>
-      <c r="F40" s="5">
+      <c r="F40" s="4">
         <v>30256</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="4">
         <v>61646</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="5">
         <v>103.3</v>
       </c>
-      <c r="I40" s="6">
+      <c r="I40" s="5">
         <v>117.6</v>
       </c>
       <c r="K40" s="1">
@@ -2331,28 +2336,28 @@
       <c r="A41" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B41" s="5">
+      <c r="B41" s="4">
         <v>35201</v>
       </c>
-      <c r="C41" s="5">
+      <c r="C41" s="4">
         <v>33792</v>
       </c>
-      <c r="D41" s="5">
+      <c r="D41" s="4">
         <v>68993</v>
       </c>
-      <c r="E41" s="5">
+      <c r="E41" s="4">
         <v>27999</v>
       </c>
-      <c r="F41" s="5">
+      <c r="F41" s="4">
         <v>26256</v>
       </c>
-      <c r="G41" s="5">
+      <c r="G41" s="4">
         <v>54255</v>
       </c>
-      <c r="H41" s="6">
+      <c r="H41" s="5">
         <v>104.2</v>
       </c>
-      <c r="I41" s="6">
+      <c r="I41" s="5">
         <v>127.2</v>
       </c>
       <c r="K41" s="1">
@@ -2376,28 +2381,28 @@
       <c r="A42" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B42" s="5">
+      <c r="B42" s="4">
         <v>25722</v>
       </c>
-      <c r="C42" s="5">
+      <c r="C42" s="4">
         <v>24249</v>
       </c>
-      <c r="D42" s="5">
+      <c r="D42" s="4">
         <v>49971</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E42" s="4">
         <v>17675</v>
       </c>
-      <c r="F42" s="5">
+      <c r="F42" s="4">
         <v>16110</v>
       </c>
-      <c r="G42" s="5">
+      <c r="G42" s="4">
         <v>33785</v>
       </c>
-      <c r="H42" s="6">
+      <c r="H42" s="5">
         <v>106.4</v>
       </c>
-      <c r="I42" s="6">
+      <c r="I42" s="5">
         <v>147.9</v>
       </c>
       <c r="K42" s="1">
@@ -2421,28 +2426,28 @@
       <c r="A43" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B43" s="5">
+      <c r="B43" s="4">
         <v>64480</v>
       </c>
-      <c r="C43" s="5">
+      <c r="C43" s="4">
         <v>61686</v>
       </c>
-      <c r="D43" s="5">
+      <c r="D43" s="4">
         <v>126166</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E43" s="4">
         <v>52782</v>
       </c>
-      <c r="F43" s="5">
+      <c r="F43" s="4">
         <v>49598</v>
       </c>
-      <c r="G43" s="5">
+      <c r="G43" s="4">
         <v>102380</v>
       </c>
-      <c r="H43" s="6">
+      <c r="H43" s="5">
         <v>104.5</v>
       </c>
-      <c r="I43" s="6">
+      <c r="I43" s="5">
         <v>123.2</v>
       </c>
       <c r="K43" s="1">
@@ -2466,28 +2471,28 @@
       <c r="A44" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="5">
+      <c r="B44" s="4">
         <v>40706</v>
       </c>
-      <c r="C44" s="5">
+      <c r="C44" s="4">
         <v>38793</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="4">
         <v>79499</v>
       </c>
-      <c r="E44" s="5">
+      <c r="E44" s="4">
         <v>33124</v>
       </c>
-      <c r="F44" s="5">
+      <c r="F44" s="4">
         <v>31186</v>
       </c>
-      <c r="G44" s="5">
+      <c r="G44" s="4">
         <v>64310</v>
       </c>
-      <c r="H44" s="6">
+      <c r="H44" s="5">
         <v>104.9</v>
       </c>
-      <c r="I44" s="6">
+      <c r="I44" s="5">
         <v>123.6</v>
       </c>
       <c r="K44" s="1">
@@ -2511,28 +2516,28 @@
       <c r="A45" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B45" s="5">
+      <c r="B45" s="4">
         <v>37370</v>
       </c>
-      <c r="C45" s="5">
+      <c r="C45" s="4">
         <v>35163</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="4">
         <v>72533</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E45" s="4">
         <v>32756</v>
       </c>
-      <c r="F45" s="5">
+      <c r="F45" s="4">
         <v>30148</v>
       </c>
-      <c r="G45" s="5">
+      <c r="G45" s="4">
         <v>62904</v>
       </c>
-      <c r="H45" s="6">
+      <c r="H45" s="5">
         <v>106.3</v>
       </c>
-      <c r="I45" s="6">
+      <c r="I45" s="5">
         <v>115.3</v>
       </c>
       <c r="K45" s="1">
@@ -2556,28 +2561,28 @@
       <c r="A46" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B46" s="5">
+      <c r="B46" s="4">
         <v>46172</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="4">
         <v>44033</v>
       </c>
-      <c r="D46" s="5">
+      <c r="D46" s="4">
         <v>90205</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E46" s="4">
         <v>28274</v>
       </c>
-      <c r="F46" s="5">
+      <c r="F46" s="4">
         <v>26709</v>
       </c>
-      <c r="G46" s="5">
+      <c r="G46" s="4">
         <v>54983</v>
       </c>
-      <c r="H46" s="6">
+      <c r="H46" s="5">
         <v>104.8</v>
       </c>
-      <c r="I46" s="6">
+      <c r="I46" s="5">
         <v>164.1</v>
       </c>
       <c r="K46" s="1">
@@ -2601,28 +2606,28 @@
       <c r="A47" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B47" s="5">
+      <c r="B47" s="4">
         <v>56810</v>
       </c>
-      <c r="C47" s="5">
+      <c r="C47" s="4">
         <v>53858</v>
       </c>
-      <c r="D47" s="5">
+      <c r="D47" s="4">
         <v>110668</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E47" s="4">
         <v>47537</v>
       </c>
-      <c r="F47" s="5">
+      <c r="F47" s="4">
         <v>44678</v>
       </c>
-      <c r="G47" s="5">
+      <c r="G47" s="4">
         <v>92215</v>
       </c>
-      <c r="H47" s="6">
+      <c r="H47" s="5">
         <v>105.5</v>
       </c>
-      <c r="I47" s="6">
+      <c r="I47" s="5">
         <v>120</v>
       </c>
       <c r="K47" s="1">
@@ -2646,28 +2651,28 @@
       <c r="A48" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B48" s="5">
+      <c r="B48" s="4">
         <v>50499</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="4">
         <v>46988</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="4">
         <v>97487</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E48" s="4">
         <v>39540</v>
       </c>
-      <c r="F48" s="5">
+      <c r="F48" s="4">
         <v>35252</v>
       </c>
-      <c r="G48" s="5">
+      <c r="G48" s="4">
         <v>74792</v>
       </c>
-      <c r="H48" s="6">
+      <c r="H48" s="5">
         <v>107.5</v>
       </c>
-      <c r="I48" s="6">
+      <c r="I48" s="5">
         <v>130.30000000000001</v>
       </c>
       <c r="K48" s="1">
@@ -2691,28 +2696,28 @@
       <c r="A49" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B49" s="5">
+      <c r="B49" s="4">
         <v>49696</v>
       </c>
-      <c r="C49" s="5">
+      <c r="C49" s="4">
         <v>49007</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="4">
         <v>98703</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E49" s="4">
         <v>37406</v>
       </c>
-      <c r="F49" s="5">
+      <c r="F49" s="4">
         <v>36118</v>
       </c>
-      <c r="G49" s="5">
+      <c r="G49" s="4">
         <v>73524</v>
       </c>
-      <c r="H49" s="6">
+      <c r="H49" s="5">
         <v>101.4</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="5">
         <v>134.19999999999999</v>
       </c>
       <c r="K49" s="1">
@@ -2736,28 +2741,28 @@
       <c r="A50" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B50" s="5">
+      <c r="B50" s="4">
         <v>5856</v>
       </c>
-      <c r="C50" s="5">
+      <c r="C50" s="4">
         <v>5702</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="4">
         <v>11558</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E50" s="4">
         <v>4530</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="4">
         <v>4325</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="4">
         <v>8855</v>
       </c>
-      <c r="H50" s="6">
+      <c r="H50" s="5">
         <v>102.7</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="5">
         <v>130.5</v>
       </c>
       <c r="K50" s="1">
@@ -2781,28 +2786,28 @@
       <c r="A51" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B51" s="5">
+      <c r="B51" s="4">
         <v>21905</v>
       </c>
-      <c r="C51" s="5">
+      <c r="C51" s="4">
         <v>20944</v>
       </c>
-      <c r="D51" s="5">
+      <c r="D51" s="4">
         <v>42849</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E51" s="4">
         <v>19045</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="4">
         <v>19140</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="4">
         <v>38185</v>
       </c>
-      <c r="H51" s="6">
+      <c r="H51" s="5">
         <v>104.6</v>
       </c>
-      <c r="I51" s="6">
+      <c r="I51" s="5">
         <v>112.2</v>
       </c>
       <c r="K51" s="1">
@@ -2823,31 +2828,31 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="4" t="s">
+      <c r="A52" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B52" s="7">
+      <c r="B52" s="10">
         <v>2014690</v>
       </c>
-      <c r="C52" s="7">
+      <c r="C52" s="10">
         <v>1911971</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="10">
         <v>3926661</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="10">
         <v>1589321</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="10">
         <v>1486941</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="10">
         <v>3076262</v>
       </c>
-      <c r="H52" s="8">
+      <c r="H52" s="11">
         <v>105.4</v>
       </c>
-      <c r="I52" s="8">
+      <c r="I52" s="11">
         <v>127.6</v>
       </c>
       <c r="K52" s="1">
@@ -2868,7 +2873,7 @@
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="9" t="s">
+      <c r="A54" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B54" s="1">
